--- a/data/Mission.xlsx
+++ b/data/Mission.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,31 +427,6 @@
           <t>condition_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>condition_id</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>mission_type</t>
@@ -478,16 +453,6 @@
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>next_mission_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>next_mission_id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t>next_mission_id</t>
         </is>
@@ -501,291 +466,187 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>bit_index</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bit_index</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>condition表的id</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1：主线，2：活动</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>自定义：非特殊情况1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0并行1顺序</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>是否自动奖励</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>condition表的id</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1：主线，2：活动</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>自定义：非特殊情况1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0并行1顺序</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>是否自动奖励</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -793,25 +654,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
         <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -820,10 +663,10 @@
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -831,13 +674,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,10 +697,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -874,7 +717,25 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -894,26 +755,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" t="n">
-        <v>19</v>
-      </c>
-      <c r="E12" t="n">
-        <v>22</v>
-      </c>
-      <c r="F12" t="n">
-        <v>24</v>
-      </c>
-      <c r="G12" t="n">
-        <v>23</v>
-      </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -928,11 +774,20 @@
       </c>
       <c r="L12" t="n">
         <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -953,21 +808,21 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -985,21 +840,21 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1017,21 +872,21 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1049,21 +904,21 @@
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -1075,30 +930,21 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>12</v>
-      </c>
-      <c r="N17" t="n">
-        <v>12</v>
-      </c>
-      <c r="O17" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1107,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -1115,13 +961,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>27</v>
+      </c>
+      <c r="C19" t="n">
+        <v>28</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -1138,19 +987,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>27</v>
-      </c>
-      <c r="C20" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1164,7 +1010,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -1173,7 +1019,7 @@
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1187,10 +1033,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -1205,29 +1051,6 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" t="n">
-        <v>29</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/Mission.xlsx
+++ b/data/Mission.xlsx
@@ -457,6 +457,11 @@
           <t>next_mission_id</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>target_count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>repeated uint32</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +551,11 @@
           <t>common</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -548,6 +563,7 @@
           <t>bit_index</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -573,6 +589,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>是否自动奖励</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>每个condition对应的目标数量(覆盖condition表默认值)</t>
         </is>
       </c>
     </row>

--- a/data/Mission.xlsx
+++ b/data/Mission.xlsx
@@ -563,7 +563,16 @@
           <t>bit_index</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gfk:Condition</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>fk:Reward</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
